--- a/inputNN/neuro_physical_model/NPM_comparison/FINAL_NPM_metrics_test.xlsx
+++ b/inputNN/neuro_physical_model/NPM_comparison/FINAL_NPM_metrics_test.xlsx
@@ -413,56 +413,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
+          <t>Дельта Х</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Дельта У</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Дельта Фи</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Проскальзывание М1</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Проскальзывание М2</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Проскальзывание М3</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Ток М1</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Ток М2</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Ток М3</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Скорость М1</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Скорость М2</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Скорость М3</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Сумма</t>
         </is>
@@ -475,34 +490,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.08570786565542221</v>
+        <v>0.004530051257461309</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0804046168923378</v>
+        <v>0.00386279821395874</v>
       </c>
       <c r="D2" t="n">
-        <v>0.09725864231586456</v>
+        <v>0.02162282168865204</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5357887744903564</v>
+        <v>0.08576709032058716</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5145588517189026</v>
+        <v>0.08064965903759003</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5693225264549255</v>
+        <v>0.09822618216276169</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05860219150781631</v>
+        <v>0.05876404047012329</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0634150430560112</v>
+        <v>0.06288840621709824</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05719444155693054</v>
+        <v>0.05740334838628769</v>
       </c>
       <c r="K2" t="n">
-        <v>2.062252998352051</v>
+        <v>0.5425761938095093</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.5149871110916138</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.5750297904014587</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.106307506561279</v>
       </c>
     </row>
     <row r="3">
@@ -512,71 +536,181 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.06323926150798798</v>
+        <v>0.004008709918707609</v>
       </c>
       <c r="C3" t="n">
-        <v>0.06298021972179413</v>
+        <v>0.003557223128154874</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07052094489336014</v>
+        <v>0.01904875598847866</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4745494723320007</v>
+        <v>0.06432637572288513</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4248560070991516</v>
+        <v>0.06268399208784103</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4768520295619965</v>
+        <v>0.07024231553077698</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04146205633878708</v>
+        <v>0.04161937534809113</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04958867654204369</v>
+        <v>0.04985915869474411</v>
       </c>
       <c r="J3" t="n">
-        <v>0.04149232059717178</v>
+        <v>0.0411270372569561</v>
       </c>
       <c r="K3" t="n">
-        <v>1.705541014671326</v>
+        <v>0.4843171536922455</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.4166310727596283</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.4669715166091919</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.724392652511597</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Разность</t>
+          <t>Обученная с нуля</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.02246860414743423</v>
+        <v>0.005509015638381243</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.01742439717054367</v>
+        <v>0.005397291854023933</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.02673769742250443</v>
+        <v>0.01991725526750088</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.06123930215835571</v>
+        <v>0.0676320418715477</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.08970284461975098</v>
+        <v>0.06571422517299652</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.09247049689292908</v>
+        <v>0.07371000200510025</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.01714013516902924</v>
+        <v>0.04304415732622147</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.01382636651396751</v>
+        <v>0.0510549433529377</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.01570212095975876</v>
+        <v>0.04239441826939583</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.3567119836807251</v>
+        <v>0.605074942111969</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.5976768732070923</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.6383885145187378</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.215513706207275</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Обученная с нуля + остаточные связи</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.004330908879637718</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.003845084924250841</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.01970039680600166</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.06434677541255951</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.06249859184026718</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.07011674344539642</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.04155576601624489</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.05014198273420334</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.0414067879319191</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.5498394966125488</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.5117971897125244</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.5925273299217224</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.012107133865356</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Разность (Скл - Трен)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.0005213413387537003</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.0003055750858038664</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.002574065700173378</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.02144071459770203</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.01796566694974899</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.02798386663198471</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.01714466512203217</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.01302924752235413</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.01627631112933159</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.05825904011726379</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.09835603833198547</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.1080582737922668</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.3819148540496826</v>
       </c>
     </row>
   </sheetData>

--- a/inputNN/neuro_physical_model/NPM_comparison/FINAL_NPM_metrics_test.xlsx
+++ b/inputNN/neuro_physical_model/NPM_comparison/FINAL_NPM_metrics_test.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,43 +490,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004530051257461309</v>
+        <v>0.00465646805241704</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00386279821395874</v>
+        <v>0.003913096152245998</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02162282168865204</v>
+        <v>0.02174774371087551</v>
       </c>
       <c r="E2" t="n">
-        <v>0.08576709032058716</v>
+        <v>0.08566854894161224</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08064965903759003</v>
+        <v>0.08057783544063568</v>
       </c>
       <c r="G2" t="n">
-        <v>0.09822618216276169</v>
+        <v>0.097529336810112</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05876404047012329</v>
+        <v>0.05867211520671844</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06288840621709824</v>
+        <v>0.06346177309751511</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05740334838628769</v>
+        <v>0.0572340153157711</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5425761938095093</v>
+        <v>0.5362322926521301</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5149871110916138</v>
+        <v>0.5148753523826599</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5750297904014587</v>
+        <v>0.5692141652107239</v>
       </c>
       <c r="N2" t="n">
-        <v>2.106307506561279</v>
+        <v>2.093782663345337</v>
       </c>
     </row>
     <row r="3">
@@ -536,43 +536,43 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004008709918707609</v>
+        <v>0.003959487657994032</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003557223128154874</v>
+        <v>0.003549219341948628</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01904875598847866</v>
+        <v>0.01906366087496281</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06432637572288513</v>
+        <v>0.06326824426651001</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06268399208784103</v>
+        <v>0.06288576871156693</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07024231553077698</v>
+        <v>0.07026173174381256</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04161937534809113</v>
+        <v>0.04160553216934204</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04985915869474411</v>
+        <v>0.05004386231303215</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0411270372569561</v>
+        <v>0.04136484861373901</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4843171536922455</v>
+        <v>0.4774965941905975</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4166310727596283</v>
+        <v>0.4165870845317841</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4669715166091919</v>
+        <v>0.4634369909763336</v>
       </c>
       <c r="N3" t="n">
-        <v>1.724392652511597</v>
+        <v>1.713523030281067</v>
       </c>
     </row>
     <row r="4">
@@ -582,43 +582,43 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.005509015638381243</v>
+        <v>0.005486858543008566</v>
       </c>
       <c r="C4" t="n">
-        <v>0.005397291854023933</v>
+        <v>0.0054101194255054</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01991725526750088</v>
+        <v>0.0198966097086668</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0676320418715477</v>
+        <v>0.06670388579368591</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06571422517299652</v>
+        <v>0.065825454890728</v>
       </c>
       <c r="G4" t="n">
-        <v>0.07371000200510025</v>
+        <v>0.07387740910053253</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04304415732622147</v>
+        <v>0.04295126721262932</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0510549433529377</v>
+        <v>0.05131732299923897</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04239441826939583</v>
+        <v>0.0424974262714386</v>
       </c>
       <c r="K4" t="n">
-        <v>0.605074942111969</v>
+        <v>0.5978816151618958</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5976768732070923</v>
+        <v>0.5972646474838257</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6383885145187378</v>
+        <v>0.6343896389007568</v>
       </c>
       <c r="N4" t="n">
-        <v>2.215513706207275</v>
+        <v>2.203502178192139</v>
       </c>
     </row>
     <row r="5">
@@ -628,89 +628,181 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.004330908879637718</v>
+        <v>0.004270743113011122</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003845084924250841</v>
+        <v>0.003834345145151019</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01970039680600166</v>
+        <v>0.01973048597574234</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06434677541255951</v>
+        <v>0.06331311166286469</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06249859184026718</v>
+        <v>0.06270965188741684</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07011674344539642</v>
+        <v>0.07017329335212708</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04155576601624489</v>
+        <v>0.04150588437914848</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05014198273420334</v>
+        <v>0.05033297836780548</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0414067879319191</v>
+        <v>0.04156428202986717</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5498394966125488</v>
+        <v>0.543082058429718</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5117971897125244</v>
+        <v>0.5127595663070679</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5925273299217224</v>
+        <v>0.5882506370544434</v>
       </c>
       <c r="N5" t="n">
-        <v>2.012107133865356</v>
+        <v>2.001527070999146</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Склеенная + остаточные связи</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.005818259436637163</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.004580957815051079</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.02544361539185047</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.096479631960392</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.08803661912679672</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1043317839503288</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.0674249678850174</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.08079832792282104</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.06949269771575928</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.4935306310653687</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.4883813261985779</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.5301328897476196</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.054451942443848</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Тренированная + остаточные связи</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.004042090382426977</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.003591873683035374</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.01920902356505394</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.06306590139865875</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.06257219612598419</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.07005096971988678</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.04158177226781845</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.04972353205084801</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.04130210727453232</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.4820400476455688</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.4348693192005157</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.5025548934936523</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.774603724479675</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Разность (Скл - Трен)</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>0.0005213413387537003</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.0003055750858038664</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.002574065700173378</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.02144071459770203</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.01796566694974899</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.02798386663198471</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.01714466512203217</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.01302924752235413</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.01627631112933159</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.05825904011726379</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.09835603833198547</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.1080582737922668</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.3819148540496826</v>
+      <c r="B8" t="n">
+        <v>0.000696980394423008</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.00036387681029737</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.002684082835912704</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.02240030467510223</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.01769206672906876</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.02726760506629944</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.0170665830373764</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.01341791078448296</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.01586916670203209</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.05873569846153259</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.09828826785087585</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.1057771742343903</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.38025963306427</v>
       </c>
     </row>
   </sheetData>
